--- a/data/trans_camb/IP19C04-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C04-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 9,69</t>
+          <t>-22,21; 9,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,28; 7,71</t>
+          <t>-24,47; 8,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,16; 13,24</t>
+          <t>-20,92; 13,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 18,11</t>
+          <t>-7,97; 18,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 12,54</t>
+          <t>-14,13; 11,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 7,44</t>
+          <t>-16,42; 6,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 11,47</t>
+          <t>-9,89; 11,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 6,31</t>
+          <t>-13,0; 5,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 5,49</t>
+          <t>-12,66; 6,79</t>
         </is>
       </c>
     </row>
@@ -783,22 +783,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 294,24</t>
+          <t>-100,0; 241,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 311,67</t>
+          <t>-100,0; 310,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 521,35</t>
+          <t>-100,0; 413,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-82,11; 802,73</t>
+          <t>-62,16; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,24 +813,24 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,48; 248,92</t>
+          <t>-62,42; 226,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-77,16; 145,75</t>
+          <t>-78,21; 129,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-83,9; 124,63</t>
+          <t>-81,38; 160,58</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 8,4</t>
+          <t>-3,79; 8,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 2,86</t>
+          <t>-7,55; 3,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 4,3</t>
+          <t>-6,89; 4,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 0,54</t>
+          <t>-10,94; 1,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 8,32</t>
+          <t>-6,54; 8,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,84; -0,23</t>
+          <t>-11,67; 0,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 2,87</t>
+          <t>-6,15; 3,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 4,14</t>
+          <t>-5,7; 3,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 0,4</t>
+          <t>-7,86; 0,38</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-72,24; 566,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,44 +1009,44 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 339,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 72,48</t>
+          <t>-100,0; 107,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-77,09; 249,22</t>
+          <t>-67,36; 296,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 90,12</t>
+          <t>-100,0; 156,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-73,87; 92,18</t>
+          <t>-75,72; 91,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,88; 121,45</t>
+          <t>-72,44; 112,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-90,46; 34,27</t>
+          <t>-92,0; 23,55</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 10,59</t>
+          <t>-11,43; 11,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,64; -2,3</t>
+          <t>-19,58; -2,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 9,4</t>
+          <t>-13,1; 9,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 5,76</t>
+          <t>-3,47; 5,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 7,42</t>
+          <t>-3,45; 8,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 12,33</t>
+          <t>-1,69; 12,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 6,21</t>
+          <t>-6,87; 6,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,0; -0,02</t>
+          <t>-10,71; -0,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 8,79</t>
+          <t>-5,4; 7,92</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-83,66; 425,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-85,44; 360,61</t>
+          <t>-87,55; 390,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-78,55; 373,88</t>
+          <t>-86,06; 292,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-59,66; 379,26</t>
+          <t>-65,37; 335,33</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 9,09</t>
+          <t>-9,67; 8,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 13,86</t>
+          <t>-6,79; 13,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 2,15</t>
+          <t>-13,71; 2,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 12,2</t>
+          <t>-4,27; 12,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 9,12</t>
+          <t>-5,32; 10,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 5,42</t>
+          <t>-7,67; 5,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 7,92</t>
+          <t>-4,68; 7,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 8,82</t>
+          <t>-3,82; 8,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 1,51</t>
+          <t>-8,4; 1,55</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-77,03; 296,88</t>
+          <t>-84,35; 258,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-60,16; 577,55</t>
+          <t>-65,93; 386,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-64,91; 277,7</t>
+          <t>-66,4; 258,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,9; 314,25</t>
+          <t>-48,25; 297,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 131,99</t>
+          <t>-100,0; 149,49</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,07</t>
+          <t>0,0; 14,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1551,37 +1551,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,8; 17,28</t>
+          <t>1,77; 15,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-21,66; 7,3</t>
+          <t>-21,28; 7,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-26,44; 3,35</t>
+          <t>-26,5; 3,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-30,74; -3,28</t>
+          <t>-31,14; -3,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 6,53</t>
+          <t>-9,67; 6,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 1,36</t>
+          <t>-12,22; 1,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 1,29</t>
+          <t>-12,28; 1,97</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 315,41</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-94,93; 490,85</t>
+          <t>-100,0; 332,95</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,14 +1687,14 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 135,89</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 8,68</t>
+          <t>-13,93; 8,29</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-14,06; 8,77</t>
+          <t>-14,86; 8,19</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 3,32</t>
+          <t>-15,81; 5,41</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 18,52</t>
+          <t>-8,64; 20,15</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 2,68</t>
+          <t>-17,09; 3,14</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-14,95; 7,98</t>
+          <t>-14,06; 7,57</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 9,75</t>
+          <t>-7,64; 10,16</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 3,26</t>
+          <t>-11,75; 3,11</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 3,42</t>
+          <t>-11,94; 3,02</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-69,36; 566,49</t>
+          <t>-63,7; 656,38</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1888,29 +1888,29 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 449,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-61,76; 225,74</t>
+          <t>-63,21; 229,64</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-84,76; 115,25</t>
+          <t>-84,83; 121,23</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-90,48; 108,33</t>
+          <t>-89,44; 134,99</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 7,94</t>
+          <t>-5,17; 8,21</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 8,72</t>
+          <t>-4,96; 7,9</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 8,94</t>
+          <t>-3,69; 8,5</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 2,54</t>
+          <t>-10,26; 1,82</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-14,34; -3,02</t>
+          <t>-14,2; -3,04</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 4,39</t>
+          <t>-8,61; 4,2</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 3,5</t>
+          <t>-5,8; 3,5</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 1,17</t>
+          <t>-7,21; 1,3</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 5,23</t>
+          <t>-4,31; 4,6</t>
         </is>
       </c>
     </row>
@@ -2079,22 +2079,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-83,82; 893,77</t>
+          <t>-80,47; 503,13</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-74,1; 567,23</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-54,05; 650,03</t>
+          <t>-60,12; 500,99</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-92,68; 164,71</t>
+          <t>-100,0; 96,72</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2104,22 +2104,22 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-78,69; 153,9</t>
+          <t>-79,74; 128,56</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-75,99; 113,61</t>
+          <t>-75,46; 115,47</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-81,31; 47,34</t>
+          <t>-83,88; 55,23</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-48,62; 172,32</t>
+          <t>-55,52; 133,15</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 6,23</t>
+          <t>-5,21; 6,45</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 5,2</t>
+          <t>-5,95; 4,99</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 1,36</t>
+          <t>-8,91; 1,33</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 3,16</t>
+          <t>-10,28; 2,07</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-12,57; -0,42</t>
+          <t>-12,63; -0,77</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-13,44; -2,91</t>
+          <t>-13,64; -2,44</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 2,49</t>
+          <t>-6,1; 2,89</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 1,09</t>
+          <t>-7,23; 0,84</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-9,32; -1,88</t>
+          <t>-8,94; -2,0</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-70,36; 281,97</t>
+          <t>-71,38; 263,63</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-77,45; 254,99</t>
+          <t>-75,54; 265,99</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 113,44</t>
+          <t>-100,0; 220,58</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-83,18; 80,55</t>
+          <t>-86,07; 59,54</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 18,55</t>
+          <t>-100,0; 16,7</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -12,95</t>
+          <t>-100,0; 12,11</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-65,35; 60,48</t>
+          <t>-64,92; 72,41</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-77,7; 31,37</t>
+          <t>-78,17; 23,35</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-95,15; -24,21</t>
+          <t>-100,0; -28,69</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 3,54</t>
+          <t>-2,28; 3,65</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 2,24</t>
+          <t>-3,43; 2,15</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 2,02</t>
+          <t>-3,96; 1,8</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 1,71</t>
+          <t>-4,17; 1,86</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-5,93; -0,43</t>
+          <t>-5,9; -0,39</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-6,55; -1,31</t>
+          <t>-6,42; -1,56</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 1,96</t>
+          <t>-2,43; 1,68</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 0,04</t>
+          <t>-3,89; 0,02</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-4,33; -0,66</t>
+          <t>-4,42; -0,68</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 76,42</t>
+          <t>-33,09; 83,34</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-44,75; 51,72</t>
+          <t>-45,9; 51,23</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-52,89; 48,5</t>
+          <t>-54,1; 41,55</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-48,69; 29,63</t>
+          <t>-49,19; 37,15</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-69,79; -6,4</t>
+          <t>-67,6; -3,83</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-74,94; -23,52</t>
+          <t>-74,75; -25,44</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-32,88; 34,52</t>
+          <t>-33,09; 32,03</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-52,74; 1,12</t>
+          <t>-51,35; 0,23</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-58,68; -11,61</t>
+          <t>-57,92; -11,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C04-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C04-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,21; 9,35</t>
+          <t>-21,9; 9,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,47; 8,96</t>
+          <t>-25,03; 8,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 13,86</t>
+          <t>-22,15; 10,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 18,47</t>
+          <t>-9,03; 19,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 11,14</t>
+          <t>-13,49; 11,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 6,77</t>
+          <t>-15,88; 6,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 11,63</t>
+          <t>-9,59; 11,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 5,86</t>
+          <t>-12,06; 6,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 6,79</t>
+          <t>-12,6; 7,2</t>
         </is>
       </c>
     </row>
@@ -783,22 +783,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 241,82</t>
+          <t>-100,0; 290,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 310,56</t>
+          <t>-100,0; 268,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 413,35</t>
+          <t>-93,2; 309,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-62,16; —</t>
+          <t>-70,16; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-62,42; 226,12</t>
+          <t>-61,47; 228,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-78,21; 129,16</t>
+          <t>-78,0; 168,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-81,38; 160,58</t>
+          <t>-81,69; 177,4</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 8,98</t>
+          <t>-4,21; 9,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 3,59</t>
+          <t>-8,72; 2,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 4,2</t>
+          <t>-7,38; 4,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 1,3</t>
+          <t>-11,13; 0,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 8,92</t>
+          <t>-6,82; 9,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 0,2</t>
+          <t>-11,62; -0,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 3,09</t>
+          <t>-6,33; 2,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 3,75</t>
+          <t>-5,41; 4,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 0,38</t>
+          <t>-7,78; 0,33</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-72,24; 566,07</t>
+          <t>-76,36; 560,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,37 +1009,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 339,83</t>
+          <t>-100,0; 490,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 107,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,36; 296,57</t>
+          <t>-68,45; 327,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 156,43</t>
+          <t>-100,0; 105,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-75,72; 91,69</t>
+          <t>-77,04; 87,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-72,44; 112,33</t>
+          <t>-71,83; 126,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-92,0; 23,55</t>
+          <t>-92,2; 37,72</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 11,84</t>
+          <t>-11,13; 12,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,58; -2,3</t>
+          <t>-20,12; -2,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 9,6</t>
+          <t>-12,88; 9,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 5,79</t>
+          <t>-4,87; 5,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 8,34</t>
+          <t>-3,47; 6,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 12,61</t>
+          <t>-1,71; 12,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 6,08</t>
+          <t>-6,58; 5,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,71; -0,05</t>
+          <t>-10,26; -0,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 7,92</t>
+          <t>-3,86; 8,72</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-87,55; 390,75</t>
+          <t>-85,47; 435,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-86,06; 292,21</t>
+          <t>-82,03; 362,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,37; 335,33</t>
+          <t>-53,57; 432,15</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 8,65</t>
+          <t>-9,13; 10,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 13,03</t>
+          <t>-8,0; 13,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 2,27</t>
+          <t>-13,85; 2,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 12,57</t>
+          <t>-4,32; 11,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 10,16</t>
+          <t>-4,53; 9,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 5,02</t>
+          <t>-7,1; 4,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 7,82</t>
+          <t>-4,74; 8,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 8,67</t>
+          <t>-3,02; 9,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 1,55</t>
+          <t>-8,83; 1,14</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-84,35; 258,72</t>
+          <t>-77,59; 373,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-65,93; 386,0</t>
+          <t>-70,28; 381,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-66,4; 258,61</t>
+          <t>-65,03; 295,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,25; 297,25</t>
+          <t>-42,92; 299,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 149,49</t>
+          <t>-100,0; 140,77</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,55</t>
+          <t>0,0; 10,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1551,37 +1551,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,77; 15,89</t>
+          <t>1,77; 15,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-21,28; 7,41</t>
+          <t>-22,37; 7,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 3,11</t>
+          <t>-25,52; 3,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-31,14; -3,26</t>
+          <t>-30,39; -3,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 6,38</t>
+          <t>-9,59; 6,65</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 1,9</t>
+          <t>-11,65; 1,91</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 1,97</t>
+          <t>-11,62; 2,11</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 315,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 332,95</t>
+          <t>-87,55; 499,38</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 8,29</t>
+          <t>-13,57; 8,08</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 8,19</t>
+          <t>-13,78; 8,54</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-15,81; 5,41</t>
+          <t>-15,48; 3,14</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 20,15</t>
+          <t>-9,43; 17,44</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-17,09; 3,14</t>
+          <t>-17,88; 1,81</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-14,06; 7,57</t>
+          <t>-13,98; 7,28</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 10,16</t>
+          <t>-6,97; 9,58</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 3,11</t>
+          <t>-10,73; 3,07</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 3,02</t>
+          <t>-11,88; 2,94</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-63,7; 656,38</t>
+          <t>-76,81; 491,76</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 138,41</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-63,21; 229,64</t>
+          <t>-58,04; 236,75</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-84,83; 121,23</t>
+          <t>-80,73; 92,79</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-89,44; 134,99</t>
+          <t>-90,79; 93,32</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 8,21</t>
+          <t>-5,24; 7,71</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 7,9</t>
+          <t>-4,94; 8,15</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 8,5</t>
+          <t>-4,19; 8,1</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 1,82</t>
+          <t>-10,15; 3,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-14,2; -3,04</t>
+          <t>-13,17; -2,99</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 4,2</t>
+          <t>-8,36; 4,74</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 3,5</t>
+          <t>-5,55; 2,88</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 1,3</t>
+          <t>-6,83; 1,08</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 4,6</t>
+          <t>-4,39; 4,69</t>
         </is>
       </c>
     </row>
@@ -2079,22 +2079,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-80,47; 503,13</t>
+          <t>-100,0; 585,78</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-74,1; 567,23</t>
+          <t>-74,96; 514,27</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-60,12; 500,99</t>
+          <t>-60,69; 551,15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 96,72</t>
+          <t>-100,0; 155,77</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2104,22 +2104,22 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-79,74; 128,56</t>
+          <t>-79,0; 157,54</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-75,46; 115,47</t>
+          <t>-73,81; 89,99</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-83,88; 55,23</t>
+          <t>-84,31; 49,6</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-55,52; 133,15</t>
+          <t>-53,78; 140,99</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 6,45</t>
+          <t>-6,05; 6,11</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 4,99</t>
+          <t>-5,77; 5,2</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 1,33</t>
+          <t>-8,32; 2,17</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 2,07</t>
+          <t>-10,51; 2,65</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-12,63; -0,77</t>
+          <t>-12,47; -0,87</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-13,64; -2,44</t>
+          <t>-13,16; -2,74</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 2,89</t>
+          <t>-6,0; 2,7</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 0,84</t>
+          <t>-7,0; 0,64</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-8,94; -2,0</t>
+          <t>-9,1; -1,93</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-71,38; 263,63</t>
+          <t>-70,69; 298,6</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-75,54; 265,99</t>
+          <t>-75,4; 230,93</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 220,58</t>
+          <t>-100,0; 244,18</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-86,07; 59,54</t>
+          <t>-82,85; 82,15</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 16,7</t>
+          <t>-100,0; 6,39</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 12,11</t>
+          <t>-100,0; 14,72</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-64,92; 72,41</t>
+          <t>-67,22; 62,98</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-78,17; 23,35</t>
+          <t>-78,35; 18,45</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -28,69</t>
+          <t>-95,83; -28,31</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 3,65</t>
+          <t>-2,38; 3,68</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 2,15</t>
+          <t>-3,13; 2,41</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 1,8</t>
+          <t>-3,75; 1,74</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 1,86</t>
+          <t>-4,42; 1,56</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-5,9; -0,39</t>
+          <t>-6,0; -0,5</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-6,42; -1,56</t>
+          <t>-6,63; -1,3</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,68</t>
+          <t>-2,59; 1,51</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 0,02</t>
+          <t>-3,76; 0,04</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-4,42; -0,68</t>
+          <t>-4,36; -0,63</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 83,34</t>
+          <t>-33,03; 91,8</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-45,9; 51,23</t>
+          <t>-44,12; 57,82</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-54,1; 41,55</t>
+          <t>-50,56; 44,19</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-49,19; 37,15</t>
+          <t>-51,94; 30,27</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-67,6; -3,83</t>
+          <t>-69,38; -7,03</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-74,75; -25,44</t>
+          <t>-75,33; -20,99</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 32,03</t>
+          <t>-35,27; 27,65</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-51,35; 0,23</t>
+          <t>-49,38; 2,17</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-57,92; -11,27</t>
+          <t>-58,21; -10,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C04-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP19C04-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,47 +624,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,57</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,39</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-2,36</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-5,12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-6,12</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-7,91</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1,02</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-2,8</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>-4,69</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,57</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-2,79</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-2,8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>-3,41</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,9; 9,27</t>
+          <t>-8,54; 18,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,03; 8,13</t>
+          <t>-13,28; 12,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 10,33</t>
+          <t>-14,09; 8,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 19,61</t>
+          <t>-22,86; 9,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 11,83</t>
+          <t>-22,28; 7,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 6,86</t>
+          <t>-26,21; 4,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 11,11</t>
+          <t>-9,12; 11,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 6,61</t>
+          <t>-12,53; 6,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 7,2</t>
+          <t>-14,85; 2,94</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>67,39%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-4,72%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-28,56%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-36,27%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-43,37%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-33,21%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>67,39%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-4,72%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-33,74%</t>
+          <t>-56,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-31,8%</t>
+          <t>-43,68%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 290,05</t>
+          <t>-82,11; 802,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 268,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-93,2; 309,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-70,16; —</t>
+          <t>-100,0; 294,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 311,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 172,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,47; 228,72</t>
+          <t>-60,48; 248,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-78,0; 168,05</t>
+          <t>-77,16; 145,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-81,69; 177,4</t>
+          <t>-84,79; 77,38</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-4,82</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-5,65</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,96</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-2,02</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,12</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-4,82</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,5</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-5,64</t>
+          <t>-0,86</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,5</t>
+          <t>-3,35</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 9,92</t>
+          <t>-11,14; 0,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 2,63</t>
+          <t>-7,15; 8,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 4,58</t>
+          <t>-11,84; -0,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 0,69</t>
+          <t>-4,55; 8,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 9,28</t>
+          <t>-6,95; 2,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,62; -0,23</t>
+          <t>-6,48; 4,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 2,75</t>
+          <t>-6,02; 2,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 4,21</t>
+          <t>-5,48; 4,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 0,33</t>
+          <t>-7,81; 0,74</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-68,33%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,07%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-80,11%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>44,78%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-46,24%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-25,7%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-68,33%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,07%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-80,04%</t>
+          <t>-19,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-60,39%</t>
+          <t>-57,79%</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-76,36; 560,43</t>
+          <t>-100,0; 72,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-77,09; 249,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 490,61</t>
+          <t>-100,0; 84,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,45; 327,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 105,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-77,04; 87,85</t>
+          <t>-73,87; 92,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,83; 126,79</t>
+          <t>-71,88; 121,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-92,2; 37,72</t>
+          <t>-89,79; 43,86</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,36</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,4</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-0,11</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-8,8</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,8</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,57</t>
+          <t>-0,97</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>1,72</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 12,47</t>
+          <t>-3,45; 5,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,12; -2,3</t>
+          <t>-3,45; 7,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 9,68</t>
+          <t>-1,73; 12,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 5,83</t>
+          <t>-11,97; 10,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 6,28</t>
+          <t>-19,64; -2,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 12,97</t>
+          <t>-12,27; 9,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 5,88</t>
+          <t>-6,46; 6,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,26; -0,11</t>
+          <t>-10,0; -0,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 8,72</t>
+          <t>-4,51; 8,7</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9,51%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21,02%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>255,46%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-1,24%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-9,07%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>21,02%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>265,3%</t>
+          <t>-11,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-85,47; 435,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-83,66; 425,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,25; 371,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-82,03; 362,5</t>
+          <t>-78,55; 373,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-53,57; 432,15</t>
+          <t>-60,2; 389,59</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,46</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-1,24</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,25</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,98</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-5,42</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,6</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,46</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,39</t>
+          <t>-5,51</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,42</t>
+          <t>-3,38</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 10,62</t>
+          <t>-4,96; 12,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 13,29</t>
+          <t>-5,0; 9,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 2,07</t>
+          <t>-7,29; 5,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 11,92</t>
+          <t>-9,03; 9,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 9,8</t>
+          <t>-5,55; 13,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 4,74</t>
+          <t>-13,56; 1,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 8,06</t>
+          <t>-4,74; 7,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 9,3</t>
+          <t>-3,51; 8,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 1,14</t>
+          <t>-8,45; 1,57</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>76,92%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>72,94%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-36,76%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>3,35%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>39,24%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-71,28%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>76,92%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>72,94%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-41,03%</t>
+          <t>-72,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-62,3%</t>
+          <t>-61,54%</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-77,59; 373,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-70,28; 381,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-77,03; 296,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-60,16; 577,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-65,03; 295,88</t>
+          <t>-64,91; 277,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-42,92; 299,85</t>
+          <t>-48,9; 314,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 140,77</t>
+          <t>-100,0; 131,32</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-6,0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-10,25</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-13,82</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>2,64</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>6,18</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-6,0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-10,25</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-13,82</t>
+          <t>6,23</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,78</t>
+          <t>-3,63</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,9</t>
+          <t>-21,66; 7,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-26,44; 3,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,77; 15,93</t>
+          <t>-30,74; -3,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 7,62</t>
+          <t>0,0; 13,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 3,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-30,39; -3,28</t>
+          <t>1,86; 17,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 6,65</t>
+          <t>-8,86; 6,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 1,91</t>
+          <t>-13,53; 1,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 2,11</t>
+          <t>-12,49; 1,51</t>
         </is>
       </c>
     </row>
@@ -1594,34 +1594,34 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-43,42%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-74,13%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-43,42%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-74,13%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
           <t>-16,83%</t>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-59,16%</t>
+          <t>-56,93%</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-87,55; 499,38</t>
+          <t>-94,93; 490,85</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 141,9</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>4,65</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-5,64</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-3,57</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-1,51</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-0,87</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-4,99</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>4,65</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-5,64</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-2,62</t>
+          <t>-5,23</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-3,85</t>
+          <t>-4,55</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 8,08</t>
+          <t>-8,62; 18,52</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 8,54</t>
+          <t>-18,53; 2,68</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-15,48; 3,14</t>
+          <t>-15,82; 6,44</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 17,44</t>
+          <t>-15,35; 8,68</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-17,88; 1,81</t>
+          <t>-14,06; 8,77</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 7,28</t>
+          <t>-18,06; 2,54</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 9,58</t>
+          <t>-8,0; 9,75</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 3,07</t>
+          <t>-11,36; 3,26</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 2,94</t>
+          <t>-12,19; 2,3</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>50,08%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-60,79%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-38,49%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-19,56%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-11,17%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-64,41%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>50,08%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-60,79%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-28,23%</t>
+          <t>-67,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-44,98%</t>
+          <t>-53,17%</t>
         </is>
       </c>
     </row>
@@ -1863,27 +1863,27 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-69,36; 566,49</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 415,52</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-76,81; 491,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 138,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-58,04; 236,75</t>
+          <t>-61,76; 225,74</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-80,73; 92,79</t>
+          <t>-84,76; 115,25</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-90,79; 93,32</t>
+          <t>-92,51; 86,82</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-3,62</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-7,08</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-1,37</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>0,82</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1,54</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>2,54</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-3,62</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-7,08</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,67</t>
+          <t>2,68</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,53</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 7,71</t>
+          <t>-10,53; 2,54</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 8,15</t>
+          <t>-14,34; -3,02</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 8,1</t>
+          <t>-8,09; 4,83</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 3,0</t>
+          <t>-5,23; 7,94</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-13,17; -2,99</t>
+          <t>-4,92; 8,72</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 4,74</t>
+          <t>-3,39; 9,08</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 2,88</t>
+          <t>-6,15; 3,5</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 1,08</t>
+          <t>-6,88; 1,17</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 4,69</t>
+          <t>-3,7; 5,65</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-51,1%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-19,29%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>18,78%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>35,05%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>57,91%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-51,1%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-23,59%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -2079,22 +2079,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 585,78</t>
+          <t>-92,68; 164,71</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-74,96; 514,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-60,69; 551,15</t>
+          <t>-76,73; 170,52</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 155,77</t>
+          <t>-83,82; 893,77</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2104,22 +2104,22 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-79,0; 157,54</t>
+          <t>-53,16; 694,7</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-73,81; 89,99</t>
+          <t>-75,99; 113,61</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-84,31; 49,6</t>
+          <t>-81,31; 47,34</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-53,78; 140,99</t>
+          <t>-47,31; 179,94</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-3,76</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-5,87</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-7,6</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>0,45</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-0,26</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-3,2</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-3,76</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-5,87</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-7,43</t>
+          <t>-3,19</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-5,3</t>
+          <t>-5,38</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 6,11</t>
+          <t>-9,74; 3,16</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 5,2</t>
+          <t>-12,57; -0,42</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 2,17</t>
+          <t>-13,49; -3,27</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 2,65</t>
+          <t>-5,27; 6,23</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-12,47; -0,87</t>
+          <t>-6,43; 5,2</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-13,16; -2,74</t>
+          <t>-8,42; 1,46</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 2,7</t>
+          <t>-6,28; 2,49</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 0,64</t>
+          <t>-7,02; 1,09</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-9,1; -1,93</t>
+          <t>-9,38; -2,1</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-44,57%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-69,53%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-90,01%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>8,68%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-5,02%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-61,15%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-44,57%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-69,53%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-88,07%</t>
+          <t>-60,94%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-78,28%</t>
+          <t>-79,4%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-70,69; 298,6</t>
+          <t>-83,18; 80,55</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-75,4; 230,93</t>
+          <t>-100,0; 18,55</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 244,18</t>
+          <t>-100,0; -26,62</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-82,85; 82,15</t>
+          <t>-70,36; 281,97</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 6,39</t>
+          <t>-77,45; 254,99</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 14,72</t>
+          <t>-100,0; 112,06</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-67,22; 62,98</t>
+          <t>-65,35; 60,48</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-78,35; 18,45</t>
+          <t>-77,7; 31,37</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-95,83; -28,31</t>
+          <t>-95,19; -28,33</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-1,35</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-3,16</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-3,95</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>0,43</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-0,57</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-1,15</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-1,35</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-3,16</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-3,86</t>
+          <t>-1,5</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-2,59</t>
+          <t>-2,78</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 3,68</t>
+          <t>-4,2; 1,71</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 2,41</t>
+          <t>-5,93; -0,43</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,74</t>
+          <t>-6,65; -1,44</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 1,56</t>
+          <t>-2,42; 3,54</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,0; -0,5</t>
+          <t>-3,16; 2,24</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-6,63; -1,3</t>
+          <t>-4,16; 1,26</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,51</t>
+          <t>-2,47; 1,96</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,04</t>
+          <t>-4,08; 0,04</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-4,36; -0,63</t>
+          <t>-4,5; -0,83</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-19,07%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-44,67%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-55,8%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>7,35%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-9,68%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-19,74%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-19,07%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-44,67%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-54,51%</t>
+          <t>-25,67%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-40,08%</t>
+          <t>-42,97%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-33,03; 91,8</t>
+          <t>-48,69; 29,63</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-44,12; 57,82</t>
+          <t>-69,79; -6,4</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-50,56; 44,19</t>
+          <t>-75,65; -24,78</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-51,94; 30,27</t>
+          <t>-33,59; 76,42</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-69,38; -7,03</t>
+          <t>-44,75; 51,72</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-75,33; -20,99</t>
+          <t>-56,75; 33,74</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-35,27; 27,65</t>
+          <t>-32,88; 34,52</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-49,38; 2,17</t>
+          <t>-52,74; 1,12</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-58,21; -10,17</t>
+          <t>-60,42; -14,97</t>
         </is>
       </c>
     </row>
